--- a/00_output/18_program_adjustments.xlsx
+++ b/00_output/18_program_adjustments.xlsx
@@ -459,11 +459,11 @@
   <dimension ref="A1:G577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
   </cols>
@@ -518,7 +518,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -4346,12 +4346,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -10001,12 +10001,12 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -10117,12 +10117,12 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -10146,12 +10146,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -11393,12 +11393,12 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -11422,12 +11422,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -11451,12 +11451,12 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -11567,12 +11567,12 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
@@ -11596,12 +11596,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -12350,12 +12350,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -12379,12 +12379,12 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
@@ -12698,12 +12698,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E423" s="4" t="inlineStr">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -12785,12 +12785,12 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E425" s="4" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E431" s="4" t="inlineStr">
@@ -12988,12 +12988,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -13017,12 +13017,12 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E433" s="4" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -13771,12 +13771,12 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E459" s="4" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -13829,12 +13829,12 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E461" s="4" t="inlineStr">
@@ -13858,12 +13858,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E463" s="4" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E465" s="4" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E467" s="4" t="inlineStr">
@@ -14032,12 +14032,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E469" s="4" t="inlineStr">
@@ -14090,12 +14090,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -14119,12 +14119,12 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E471" s="4" t="inlineStr">
@@ -14148,12 +14148,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E473" s="4" t="inlineStr">
@@ -14206,12 +14206,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -14235,12 +14235,12 @@
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E475" s="4" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E477" s="4" t="inlineStr">
@@ -14322,12 +14322,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -14351,12 +14351,12 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E479" s="4" t="inlineStr">
@@ -14380,12 +14380,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E481" s="4" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -15134,12 +15134,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -15163,12 +15163,12 @@
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E507" s="4" t="inlineStr">
@@ -15192,12 +15192,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -15221,12 +15221,12 @@
       </c>
       <c r="C509" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D509" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E509" s="4" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -15279,12 +15279,12 @@
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D511" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E511" s="4" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -15337,12 +15337,12 @@
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D513" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E513" s="4" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -15395,12 +15395,12 @@
       </c>
       <c r="C515" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D515" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E515" s="4" t="inlineStr">
@@ -15424,12 +15424,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="C517" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D517" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E517" s="4" t="inlineStr">
@@ -15482,12 +15482,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="C519" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D519" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E519" s="4" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -15569,12 +15569,12 @@
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D521" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E521" s="4" t="inlineStr">
@@ -15598,12 +15598,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D523" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E523" s="4" t="inlineStr">
@@ -15656,12 +15656,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -15685,12 +15685,12 @@
       </c>
       <c r="C525" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D525" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E525" s="4" t="inlineStr">
@@ -15714,12 +15714,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="C527" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D527" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E527" s="4" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -15801,12 +15801,12 @@
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D529" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E529" s="4" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D531" s="4" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D533" s="4" t="inlineStr">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D535" s="4" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D537" s="4" t="inlineStr">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D539" s="4" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D541" s="4" t="inlineStr">
@@ -16526,12 +16526,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
@@ -16555,12 +16555,12 @@
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D555" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E555" s="4" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
@@ -16613,12 +16613,12 @@
       </c>
       <c r="C557" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D557" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E557" s="4" t="inlineStr">
@@ -16642,12 +16642,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -16671,12 +16671,12 @@
       </c>
       <c r="C559" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D559" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E559" s="4" t="inlineStr">
@@ -16700,12 +16700,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -16729,12 +16729,12 @@
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D561" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E561" s="4" t="inlineStr">
@@ -16758,12 +16758,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
@@ -16787,12 +16787,12 @@
       </c>
       <c r="C563" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E563" s="4" t="inlineStr">
@@ -16816,12 +16816,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="C565" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="D565" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="E565" s="4" t="inlineStr">
@@ -16874,12 +16874,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="C567" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D567" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E567" s="4" t="inlineStr">
@@ -16932,12 +16932,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="C569" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D569" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E569" s="4" t="inlineStr">
@@ -16990,12 +16990,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="C571" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E571" s="4" t="inlineStr">
@@ -17048,12 +17048,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -17077,12 +17077,12 @@
       </c>
       <c r="C573" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D573" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E573" s="4" t="inlineStr">
@@ -17106,12 +17106,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -17135,12 +17135,12 @@
       </c>
       <c r="C575" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D575" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E575" s="4" t="inlineStr">
@@ -17164,12 +17164,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="D577" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="E577" s="4" t="inlineStr">
